--- a/order-helper-backend/data/总库存.xlsx
+++ b/order-helper-backend/data/总库存.xlsx
@@ -1795,7 +1795,7 @@
     <t>JYW004</t>
   </si>
   <si>
-    <t>JY-410A黑色</t>
+    <t>JY-410A黑</t>
   </si>
   <si>
     <t>QX-000030</t>
@@ -1807,7 +1807,7 @@
     <t>QX-0000300023</t>
   </si>
   <si>
-    <t>JY-410A白色</t>
+    <t>JY-410A白</t>
   </si>
   <si>
     <t>QX-0000300022</t>
